--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484150_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484150_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.4649</v>
+        <v>4.6317</v>
       </c>
       <c r="E2" t="n">
-        <v>2.6353</v>
+        <v>3.7179</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8296</v>
+        <v>0.9137999999999999</v>
       </c>
       <c r="G2" t="n">
         <v>4.5962</v>
@@ -610,13 +610,13 @@
         <v>2.7774</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.5163</v>
+        <v>0.6505</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.6574</v>
+        <v>0.4253</v>
       </c>
       <c r="U2" t="n">
-        <v>0.141</v>
+        <v>0.2252</v>
       </c>
       <c r="V2" t="n">
         <v>-1.0118</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.7881</v>
+        <v>2.2663</v>
       </c>
       <c r="E3" t="n">
-        <v>3.8393</v>
+        <v>3.2894</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.0512</v>
+        <v>-1.0231</v>
       </c>
       <c r="G3" t="n">
         <v>-0.4643</v>
@@ -688,13 +688,13 @@
         <v>1.1903</v>
       </c>
       <c r="S3" t="n">
-        <v>1.9232</v>
+        <v>1.4015</v>
       </c>
       <c r="T3" t="n">
-        <v>1.4512</v>
+        <v>0.9013</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4721</v>
+        <v>0.5001</v>
       </c>
       <c r="V3" t="n">
         <v>0.3373</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.5534</v>
+        <v>1.5775</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.7945</v>
+        <v>-0.6301</v>
       </c>
       <c r="F4" t="n">
-        <v>2.3479</v>
+        <v>2.2076</v>
       </c>
       <c r="G4" t="n">
         <v>-1.1494</v>
@@ -766,13 +766,13 @@
         <v>1.7855</v>
       </c>
       <c r="S4" t="n">
-        <v>0.7624</v>
+        <v>0.7865</v>
       </c>
       <c r="T4" t="n">
-        <v>0.3856</v>
+        <v>0.5499000000000001</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3768</v>
+        <v>0.2365</v>
       </c>
       <c r="V4" t="n">
         <v>1.5437</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.373</v>
+        <v>0.2607</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>0.373</v>
+        <v>0.2607</v>
       </c>
       <c r="G5" t="n">
         <v>0.136</v>
@@ -844,13 +844,13 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>0.2369</v>
+        <v>0.1247</v>
       </c>
       <c r="T5" t="n">
         <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2369</v>
+        <v>0.1247</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. LATORRE SEGURA</t>
+          <t>B. ENRICH TASIAS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,58 +877,58 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.9624</v>
+        <v>-1.1092</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.1617</v>
+        <v>-0.2393</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.8007</v>
+        <v>-0.87</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.5139</v>
+        <v>-1.3388</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.6148</v>
+        <v>-1.1445</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.8991</v>
+        <v>-0.1943</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.6549</v>
+        <v>0.3218</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.0149</v>
+        <v>0.121</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.64</v>
+        <v>0.2008</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.859</v>
+        <v>-1.6606</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.6</v>
+        <v>-1.2655</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.2591</v>
+        <v>-0.3951</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>-0.3968</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-0.9919</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>0.5952</v>
       </c>
       <c r="S6" t="n">
-        <v>0.5515</v>
+        <v>0.6264</v>
       </c>
       <c r="T6" t="n">
-        <v>0.4932</v>
+        <v>0.4309</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0584</v>
+        <v>0.1955</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>B. ENRICH TASIAS</t>
+          <t>L. SALA MAS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.2674</v>
+        <v>-1.1274</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.3413</v>
+        <v>-1.8058</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.9261</v>
+        <v>0.6783</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.3388</v>
+        <v>-2.4631</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.1445</v>
+        <v>0.2059</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1943</v>
+        <v>-2.669</v>
       </c>
       <c r="J7" t="n">
-        <v>0.3218</v>
+        <v>-1.6415</v>
       </c>
       <c r="K7" t="n">
-        <v>0.121</v>
+        <v>0.5093</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2008</v>
+        <v>-2.1509</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.6606</v>
+        <v>-0.8216</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.2655</v>
+        <v>-0.3035</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.3951</v>
+        <v>-0.5182</v>
       </c>
       <c r="P7" t="n">
+        <v>1.9838</v>
+      </c>
+      <c r="Q7" t="n">
         <v>-0.3968</v>
       </c>
-      <c r="Q7" t="n">
-        <v>-0.9919</v>
-      </c>
       <c r="R7" t="n">
-        <v>0.5952</v>
+        <v>2.3806</v>
       </c>
       <c r="S7" t="n">
-        <v>0.4682</v>
+        <v>0.5583</v>
       </c>
       <c r="T7" t="n">
-        <v>0.3288</v>
+        <v>0.2325</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1394</v>
+        <v>0.3258</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-1.2065</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-1.2065</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>L. SALA MAS</t>
+          <t>A. LATORRE SEGURA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.0099</v>
+        <v>-1.3425</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.52</v>
+        <v>-0.5699</v>
       </c>
       <c r="F8" t="n">
-        <v>0.51</v>
+        <v>-0.7726</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.4631</v>
+        <v>-1.5139</v>
       </c>
       <c r="H8" t="n">
-        <v>0.2059</v>
+        <v>-0.6148</v>
       </c>
       <c r="I8" t="n">
-        <v>-2.669</v>
+        <v>-0.8991</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.6415</v>
+        <v>-0.6549</v>
       </c>
       <c r="K8" t="n">
-        <v>0.5093</v>
+        <v>-0.0149</v>
       </c>
       <c r="L8" t="n">
-        <v>-2.1509</v>
+        <v>-0.64</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.8216</v>
+        <v>-0.859</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.3035</v>
+        <v>-0.6</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.5182</v>
+        <v>-0.2591</v>
       </c>
       <c r="P8" t="n">
-        <v>1.9838</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.3968</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2.3806</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.3242</v>
+        <v>0.1714</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.4817</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1575</v>
+        <v>0.0864</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.2065</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.2065</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.723</v>
+        <v>-2.9285</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.8783</v>
+        <v>-4.2241</v>
       </c>
       <c r="F9" t="n">
-        <v>1.1553</v>
+        <v>1.2955</v>
       </c>
       <c r="G9" t="n">
         <v>-1.0013</v>
@@ -1156,13 +1156,13 @@
         <v>2.7774</v>
       </c>
       <c r="S9" t="n">
-        <v>0.6831</v>
+        <v>0.4776</v>
       </c>
       <c r="T9" t="n">
-        <v>0.6803</v>
+        <v>0.3346</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0027</v>
+        <v>0.143</v>
       </c>
       <c r="V9" t="n">
         <v>-1.8097</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.7842</v>
+        <v>-3.4845</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.6144</v>
+        <v>-4.0622</v>
       </c>
       <c r="F10" t="n">
-        <v>0.8302</v>
+        <v>0.5777</v>
       </c>
       <c r="G10" t="n">
         <v>-3.259</v>
@@ -1234,13 +1234,13 @@
         <v>2.3806</v>
       </c>
       <c r="S10" t="n">
-        <v>1.0333</v>
+        <v>0.333</v>
       </c>
       <c r="T10" t="n">
-        <v>0.6917</v>
+        <v>0.2439</v>
       </c>
       <c r="U10" t="n">
-        <v>0.3416</v>
+        <v>0.0891</v>
       </c>
       <c r="V10" t="n">
         <v>3.2109</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.5675</v>
+        <v>-1.2559</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.835599999999999</v>
+        <v>-4.524099999999999</v>
       </c>
       <c r="F11" t="n">
-        <v>3.268</v>
+        <v>3.2679</v>
       </c>
       <c r="G11" t="n">
         <v>-6.457599999999999</v>
@@ -1285,7 +1285,7 @@
         <v>-4.1137</v>
       </c>
       <c r="J11" t="n">
-        <v>2.273500000000001</v>
+        <v>2.2735</v>
       </c>
       <c r="K11" t="n">
         <v>1.8208</v>
@@ -1312,13 +1312,13 @@
         <v>13.887</v>
       </c>
       <c r="S11" t="n">
-        <v>4.8181</v>
+        <v>5.1299</v>
       </c>
       <c r="T11" t="n">
-        <v>2.8917</v>
+        <v>3.2034</v>
       </c>
       <c r="U11" t="n">
-        <v>1.9264</v>
+        <v>1.9263</v>
       </c>
       <c r="V11" t="n">
         <v>1.0639</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>3.3706</v>
+        <v>3.3196</v>
       </c>
       <c r="E12" t="n">
-        <v>1.5024</v>
+        <v>1.6045</v>
       </c>
       <c r="F12" t="n">
-        <v>1.8681</v>
+        <v>1.7151</v>
       </c>
       <c r="G12" t="n">
         <v>2.131</v>
@@ -1390,13 +1390,13 @@
         <v>1.7855</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.2268</v>
+        <v>-0.2778</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.3683</v>
+        <v>-0.2663</v>
       </c>
       <c r="U12" t="n">
-        <v>0.1415</v>
+        <v>-0.0115</v>
       </c>
       <c r="V12" t="n">
         <v>-0.1206</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>B. BONET TORRALBA</t>
+          <t>E. NOGUES MARTIN</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.168</v>
+        <v>2.8439</v>
       </c>
       <c r="E13" t="n">
-        <v>0.8034</v>
+        <v>-0.2292</v>
       </c>
       <c r="F13" t="n">
-        <v>2.3647</v>
+        <v>3.0731</v>
       </c>
       <c r="G13" t="n">
-        <v>1.1079</v>
+        <v>0.5427</v>
       </c>
       <c r="H13" t="n">
+        <v>-1.3398</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1.8825</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.4153</v>
+      </c>
+      <c r="K13" t="n">
+        <v>-1.4347</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.1274</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.0949</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.0325</v>
+      </c>
+      <c r="P13" t="n">
+        <v>1.3887</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>-1.1903</v>
+      </c>
+      <c r="R13" t="n">
+        <v>2.579</v>
+      </c>
+      <c r="S13" t="n">
+        <v>-0.7765</v>
+      </c>
+      <c r="T13" t="n">
         <v>-0.5894</v>
       </c>
-      <c r="I13" t="n">
-        <v>1.6972</v>
-      </c>
-      <c r="J13" t="n">
-        <v>1.0639</v>
-      </c>
-      <c r="K13" t="n">
-        <v>-0.3417</v>
-      </c>
-      <c r="L13" t="n">
-        <v>1.4057</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0.0439</v>
-      </c>
-      <c r="N13" t="n">
-        <v>-0.2477</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0.2916</v>
-      </c>
-      <c r="P13" t="n">
-        <v>-0.3968</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>-2.1822</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1.7855</v>
-      </c>
-      <c r="S13" t="n">
-        <v>3.0602</v>
-      </c>
-      <c r="T13" t="n">
-        <v>1.9216</v>
-      </c>
       <c r="U13" t="n">
-        <v>1.1385</v>
+        <v>-0.1872</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.6032</v>
+        <v>1.689</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.1352</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.6032</v>
+        <v>0.5538999999999999</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>E. NOGUES MARTIN</t>
+          <t>M. GARCIA IBAÑEZ</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.4698</v>
+        <v>2.037</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.3312</v>
+        <v>2.2255</v>
       </c>
       <c r="F14" t="n">
-        <v>2.801</v>
+        <v>-0.1885</v>
       </c>
       <c r="G14" t="n">
-        <v>0.5427</v>
+        <v>2.7277</v>
       </c>
       <c r="H14" t="n">
-        <v>-1.3398</v>
+        <v>0.6755</v>
       </c>
       <c r="I14" t="n">
-        <v>1.8825</v>
+        <v>2.0522</v>
       </c>
       <c r="J14" t="n">
-        <v>0.4153</v>
+        <v>2.8133</v>
       </c>
       <c r="K14" t="n">
-        <v>-1.4347</v>
+        <v>0.9232</v>
       </c>
       <c r="L14" t="n">
-        <v>1.85</v>
+        <v>1.8901</v>
       </c>
       <c r="M14" t="n">
-        <v>0.1274</v>
+        <v>-0.0856</v>
       </c>
       <c r="N14" t="n">
-        <v>0.0949</v>
+        <v>-0.2477</v>
       </c>
       <c r="O14" t="n">
-        <v>0.0325</v>
+        <v>0.162</v>
       </c>
       <c r="P14" t="n">
-        <v>1.3887</v>
+        <v>-0.1984</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.1903</v>
+        <v>-1.9838</v>
       </c>
       <c r="R14" t="n">
-        <v>2.579</v>
+        <v>1.7855</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.1507</v>
+        <v>-0.9749</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.6914</v>
+        <v>-0.4137</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.4593</v>
+        <v>-0.5613</v>
       </c>
       <c r="V14" t="n">
-        <v>1.689</v>
+        <v>0.4826</v>
       </c>
       <c r="W14" t="n">
-        <v>1.1352</v>
+        <v>1.8097</v>
       </c>
       <c r="X14" t="n">
-        <v>0.5538999999999999</v>
+        <v>-1.3271</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>M. GARCIA IBAÑEZ</t>
+          <t>I. VILLAR CANTERO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.2548</v>
+        <v>1.5378</v>
       </c>
       <c r="E15" t="n">
-        <v>1.7153</v>
+        <v>-0.2176</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.4606</v>
+        <v>1.7554</v>
       </c>
       <c r="G15" t="n">
-        <v>2.7277</v>
+        <v>-0.1956</v>
       </c>
       <c r="H15" t="n">
-        <v>0.6755</v>
+        <v>1.8345</v>
       </c>
       <c r="I15" t="n">
-        <v>2.0522</v>
+        <v>-2.0301</v>
       </c>
       <c r="J15" t="n">
-        <v>2.8133</v>
+        <v>0.026</v>
       </c>
       <c r="K15" t="n">
-        <v>0.9232</v>
+        <v>1.9461</v>
       </c>
       <c r="L15" t="n">
-        <v>1.8901</v>
+        <v>-1.9201</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.0856</v>
+        <v>-0.2216</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.2477</v>
+        <v>-0.1116</v>
       </c>
       <c r="O15" t="n">
-        <v>0.162</v>
+        <v>-0.11</v>
       </c>
       <c r="P15" t="n">
+        <v>1.7855</v>
+      </c>
+      <c r="Q15" t="n">
         <v>-0.1984</v>
       </c>
-      <c r="Q15" t="n">
-        <v>-1.9838</v>
-      </c>
       <c r="R15" t="n">
-        <v>1.7855</v>
+        <v>1.9838</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.7572</v>
+        <v>0.214</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.9238</v>
+        <v>-0.0452</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.8333</v>
+        <v>0.2592</v>
       </c>
       <c r="V15" t="n">
-        <v>0.4826</v>
+        <v>-0.266</v>
       </c>
       <c r="W15" t="n">
-        <v>1.8097</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.3271</v>
+        <v>-0.266</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>P. MORENO MARTIN</t>
+          <t>B. BONET TORRALBA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,64 +1657,64 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.02</v>
+        <v>1.3222</v>
       </c>
       <c r="E16" t="n">
-        <v>1.8625</v>
+        <v>-0.421</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.8424</v>
+        <v>1.7432</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.3059</v>
+        <v>1.1079</v>
       </c>
       <c r="H16" t="n">
-        <v>0.3678</v>
+        <v>-0.5894</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.6737</v>
+        <v>1.6972</v>
       </c>
       <c r="J16" t="n">
-        <v>0.2876</v>
+        <v>1.0639</v>
       </c>
       <c r="K16" t="n">
-        <v>0.9678</v>
+        <v>-0.3417</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.6802</v>
+        <v>1.4057</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.5935</v>
+        <v>0.0439</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.6</v>
+        <v>-0.2477</v>
       </c>
       <c r="O16" t="n">
-        <v>0.0065</v>
+        <v>0.2916</v>
       </c>
       <c r="P16" t="n">
-        <v>0.3968</v>
+        <v>-0.3968</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-2.1822</v>
       </c>
       <c r="R16" t="n">
-        <v>0.3968</v>
+        <v>1.7855</v>
       </c>
       <c r="S16" t="n">
-        <v>0.3259</v>
+        <v>1.2144</v>
       </c>
       <c r="T16" t="n">
-        <v>0.3685</v>
+        <v>0.6973</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.0425</v>
+        <v>0.5171</v>
       </c>
       <c r="V16" t="n">
-        <v>0.6032</v>
+        <v>-0.6032</v>
       </c>
       <c r="W16" t="n">
-        <v>1.2065</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
         <v>-0.6032</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>I. VILLAR CANTERO</t>
+          <t>P. MORENO MARTIN</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.1647</v>
+        <v>0.7522</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.0339</v>
+        <v>1.4544</v>
       </c>
       <c r="F17" t="n">
-        <v>1.1986</v>
+        <v>-0.7022</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.1956</v>
+        <v>-0.3059</v>
       </c>
       <c r="H17" t="n">
-        <v>1.8345</v>
+        <v>0.3678</v>
       </c>
       <c r="I17" t="n">
-        <v>-2.0301</v>
+        <v>-0.6737</v>
       </c>
       <c r="J17" t="n">
-        <v>0.026</v>
+        <v>0.2876</v>
       </c>
       <c r="K17" t="n">
-        <v>1.9461</v>
+        <v>0.9678</v>
       </c>
       <c r="L17" t="n">
-        <v>-1.9201</v>
+        <v>-0.6802</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.2216</v>
+        <v>-0.5935</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.1116</v>
+        <v>-0.6</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.11</v>
+        <v>0.0065</v>
       </c>
       <c r="P17" t="n">
-        <v>1.7855</v>
+        <v>0.3968</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.1984</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.9838</v>
+        <v>0.3968</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.1591</v>
+        <v>0.0581</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.8615</v>
+        <v>-0.0396</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.2976</v>
+        <v>0.0978</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.266</v>
+        <v>0.6032</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.2065</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.266</v>
+        <v>-0.6032</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. ESONO MBA</t>
+          <t>L. MARTÍN LLAVERÍA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.3284</v>
+        <v>-0.6935</v>
       </c>
       <c r="E18" t="n">
-        <v>1.0624</v>
+        <v>-1.0718</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.3908</v>
+        <v>0.3783</v>
       </c>
       <c r="G18" t="n">
-        <v>0.6491</v>
+        <v>0.3283</v>
       </c>
       <c r="H18" t="n">
-        <v>1.0533</v>
+        <v>0.1055</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.4042</v>
+        <v>0.2229</v>
       </c>
       <c r="J18" t="n">
-        <v>1.0935</v>
+        <v>0.6909</v>
       </c>
       <c r="K18" t="n">
-        <v>0.9731</v>
+        <v>0.0859</v>
       </c>
       <c r="L18" t="n">
-        <v>0.1205</v>
+        <v>0.605</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.4444</v>
+        <v>-0.3626</v>
       </c>
       <c r="N18" t="n">
-        <v>0.08019999999999999</v>
+        <v>0.0195</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.5247000000000001</v>
+        <v>-0.3821</v>
       </c>
       <c r="P18" t="n">
         <v>0.3968</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-0.9919</v>
       </c>
       <c r="R18" t="n">
-        <v>0.3968</v>
+        <v>1.3887</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.5152</v>
+        <v>-1.298</v>
       </c>
       <c r="T18" t="n">
-        <v>0.3061</v>
+        <v>-0.7708</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.8213</v>
+        <v>-0.5272</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.8591</v>
+        <v>-0.1206</v>
       </c>
       <c r="W18" t="n">
-        <v>-0.3373</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.5218</v>
+        <v>-0.1206</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>L. MARTÍN LLAVERÍA</t>
+          <t>J. ESONO MBA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.4043</v>
+        <v>-1.2681</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.1738</v>
+        <v>0.6543</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.2305</v>
+        <v>-1.9223</v>
       </c>
       <c r="G19" t="n">
-        <v>0.3283</v>
+        <v>0.6491</v>
       </c>
       <c r="H19" t="n">
-        <v>0.1055</v>
+        <v>1.0533</v>
       </c>
       <c r="I19" t="n">
-        <v>0.2229</v>
+        <v>-0.4042</v>
       </c>
       <c r="J19" t="n">
-        <v>0.6909</v>
+        <v>1.0935</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0859</v>
+        <v>0.9731</v>
       </c>
       <c r="L19" t="n">
-        <v>0.605</v>
+        <v>0.1205</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.3626</v>
+        <v>-0.4444</v>
       </c>
       <c r="N19" t="n">
-        <v>0.0195</v>
+        <v>0.08019999999999999</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.3821</v>
+        <v>-0.5247000000000001</v>
       </c>
       <c r="P19" t="n">
         <v>0.3968</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.9919</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.3887</v>
+        <v>0.3968</v>
       </c>
       <c r="S19" t="n">
-        <v>-2.0088</v>
+        <v>-0.4549</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.8728</v>
+        <v>-0.102</v>
       </c>
       <c r="U19" t="n">
-        <v>-1.1359</v>
+        <v>-0.3529</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.1206</v>
+        <v>-1.8591</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>-0.3373</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.1206</v>
+        <v>-1.5218</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.434</v>
+        <v>-1.9996</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.4225</v>
+        <v>-0.3205</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.0115</v>
+        <v>-1.6791</v>
       </c>
       <c r="G20" t="n">
         <v>1.2205</v>
@@ -2014,13 +2014,13 @@
         <v>0.3968</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.861</v>
+        <v>-0.4265</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.3117</v>
+        <v>-0.2097</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.5493</v>
+        <v>-0.2168</v>
       </c>
       <c r="V20" t="n">
         <v>-1.2065</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.7135</v>
+        <v>-4.2433</v>
       </c>
       <c r="E21" t="n">
-        <v>-7.2526</v>
+        <v>-6.9465</v>
       </c>
       <c r="F21" t="n">
-        <v>2.5391</v>
+        <v>2.7032</v>
       </c>
       <c r="G21" t="n">
         <v>-1.7479</v>
@@ -2092,13 +2092,13 @@
         <v>2.3806</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.5255</v>
+        <v>-0.0553</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.493</v>
+        <v>-0.1869</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0324</v>
+        <v>0.1317</v>
       </c>
       <c r="V21" t="n">
         <v>0.3373</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>1.567700000000001</v>
+        <v>3.608199999999999</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.268</v>
+        <v>-3.267900000000001</v>
       </c>
       <c r="F22" t="n">
-        <v>4.835699999999999</v>
+        <v>6.8762</v>
       </c>
       <c r="G22" t="n">
         <v>6.457800000000001</v>
@@ -2140,7 +2140,7 @@
         <v>2.344</v>
       </c>
       <c r="I22" t="n">
-        <v>4.1137</v>
+        <v>4.113700000000001</v>
       </c>
       <c r="J22" t="n">
         <v>8.731</v>
@@ -2158,10 +2158,10 @@
         <v>-1.8209</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.4526999999999999</v>
+        <v>-0.4527</v>
       </c>
       <c r="P22" t="n">
-        <v>0.9920000000000004</v>
+        <v>0.9919999999999995</v>
       </c>
       <c r="Q22" t="n">
         <v>-13.8868</v>
@@ -2170,13 +2170,13 @@
         <v>14.879</v>
       </c>
       <c r="S22" t="n">
-        <v>-4.8182</v>
+        <v>-2.7774</v>
       </c>
       <c r="T22" t="n">
         <v>-1.9263</v>
       </c>
       <c r="U22" t="n">
-        <v>-2.8916</v>
+        <v>-0.8511</v>
       </c>
       <c r="V22" t="n">
         <v>-1.0639</v>
